--- a/apiHirams/resources/templates/POTemplate.xlsx
+++ b/apiHirams/resources/templates/POTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Files\Program\hirams\apiHirams\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8B2F8D0-5F4F-46E7-9FFB-E8D15B97BC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E5F654-BF8F-4C17-A0D1-64B69B7C9DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5391CC67-D73C-4521-B7F6-16F3EA47EC1F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <t>Qty</t>
   </si>
@@ -123,21 +123,6 @@
   </si>
   <si>
     <t>PAYABLE AMOUNT</t>
-  </si>
-  <si>
-    <t>COMPANY NAME</t>
-  </si>
-  <si>
-    <t>Tin</t>
-  </si>
-  <si>
-    <t>Contact No.</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Address</t>
   </si>
   <si>
     <t>GM NAME</t>
@@ -1359,9 +1344,7 @@
   <sheetData>
     <row r="1" spans="2:14" ht="4.8" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:14" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B2" s="36" t="s">
-        <v>28</v>
-      </c>
+      <c r="B2" s="36"/>
       <c r="C2" s="36"/>
       <c r="D2" s="36"/>
       <c r="E2" s="36"/>
@@ -1371,9 +1354,7 @@
       <c r="I2" s="37"/>
     </row>
     <row r="3" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="92" t="s">
-        <v>32</v>
-      </c>
+      <c r="B3" s="92"/>
       <c r="C3" s="92"/>
       <c r="D3" s="92"/>
       <c r="E3" s="92"/>
@@ -1383,9 +1364,7 @@
       <c r="I3" s="38"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="93" t="s">
-        <v>31</v>
-      </c>
+      <c r="B4" s="93"/>
       <c r="C4" s="93"/>
       <c r="D4" s="93"/>
       <c r="E4" s="94"/>
@@ -1397,9 +1376,7 @@
       <c r="I4" s="91"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B5" s="66" t="s">
-        <v>30</v>
-      </c>
+      <c r="B5" s="66"/>
       <c r="C5" s="66"/>
       <c r="D5" s="66"/>
       <c r="E5" s="67"/>
@@ -1413,9 +1390,7 @@
       <c r="I5" s="35"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B6" s="66" t="s">
-        <v>29</v>
-      </c>
+      <c r="B6" s="66"/>
       <c r="C6" s="66"/>
       <c r="D6" s="66"/>
       <c r="E6" s="67"/>
@@ -1441,7 +1416,7 @@
       <c r="H8" s="40"/>
       <c r="I8" s="41"/>
     </row>
-    <row r="9" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:14" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="63"/>
       <c r="C9" s="64"/>
       <c r="D9" s="64"/>
@@ -1641,14 +1616,14 @@
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27" s="45" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C27" s="45"/>
       <c r="D27" s="25" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E27" s="45" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F27" s="45"/>
       <c r="G27" s="45"/>
@@ -1751,10 +1726,7 @@
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B5:E5"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1" display="hirams_supplies@yahoo.com" xr:uid="{E561545B-5732-499F-9190-7354C0FBD2B7}"/>
-  </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>